--- a/checklist_forms/029_marketing_plan_evaluation_checklist--checklist_forms.xlsx
+++ b/checklist_forms/029_marketing_plan_evaluation_checklist--checklist_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,12 +1102,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
-    <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="37" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1135,12 +1135,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1152,12 +1152,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'marketing_mix'}</t>
+          <t>marketing_mix</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Marketing Mix'}</t>
+          <t>Marketing Mix</t>
         </is>
       </c>
     </row>
@@ -1186,29 +1186,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'marketing_mix'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Marketing Mix'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>marketing_mix_choices</t>
+          <t>marketing_budget_allocation_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'marketing_mix'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Marketing Mix'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1220,29 +1220,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>marketing_budget_allocation_choices</t>
+          <t>evaluation_status_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -1254,12 +1254,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'completed'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Completed'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -1271,29 +1271,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'in_progress'}</t>
+          <t>on_hold</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'In Progress'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>evaluation_status_choices</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>{'id':_3,_'label':_'on_hold'}</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>{'id': 3, 'label': 'On Hold'}</t>
+          <t>On Hold</t>
         </is>
       </c>
     </row>
